--- a/www/download/IND.gross_output.s.du.rpPE.xlsx
+++ b/www/download/IND.gross_output.s.du.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168078.083403275</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172625.265106987</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170647.841906956</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171332.704048245</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189746.575312446</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189233.933724555</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179465.841829906</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193779.184735759</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217242.922028606</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261553.817455386</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286708.627896018</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304388.973987529</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356161.710725031</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>408541.055922305</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>390011.564014018</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102358.111201433</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105298.114868402</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98322.5792777345</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100209.827377216</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105645.235062518</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111089.791956733</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110637.897499967</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111320.409491336</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120596.970506052</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140457.623550277</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147159.651848412</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162326.810251226</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184759.83452902</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187143.648287336</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>153254.100960532</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113032.846440485</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107916.763659581</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101139.589422996</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102534.061506838</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109238.741468038</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120350.45390887</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116555.64725831</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115730.744352165</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132681.789815261</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155662.577117741</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161805.500640972</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180565.041372019</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209914.894423553</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>267421.338725078</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192576.070322288</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51360.5200157128</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53489.2652284979</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46082.7234855031</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41961.7363557934</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44227.5756018298</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39081.2954004628</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34981.23108593</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35202.4424820932</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41321.7424314615</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49005.6341404493</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52918.8994902277</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60751.8627146495</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72956.4850284986</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84453.565017108</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78425.5444392503</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>1015359.62777713</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1027000.74699889</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>1024726.59607504</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1002432.05844708</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1065889.5174277</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1138322.2353938</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>1100702.6441668</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.163</t>
+          <t>1163109.41646689</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1315484.54539141</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1514363.91384996</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>1679054.71027537</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>1807613.71087563</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>2145195.08053347</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.497</t>
+          <t>2496883.86501265</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.278</t>
+          <t>2277547.07684242</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>330338.181300517</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>335099.702117867</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>330907.102249579</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>332838.595877682</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>361433.435377154</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>397665.560635811</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>384726.707513896</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377989.731722573</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>412864.277788812</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485636.257915145</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>530173.927254598</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566872.540833784</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>618459.525748329</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>682172.961025653</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>594612.910190819</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10.711</t>
+          <t>10711305.5574487</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.204</t>
+          <t>11203764.7954147</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.228</t>
+          <t>11228163.0610612</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10.863</t>
+          <t>10862822.6648637</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.169</t>
+          <t>11168853.6957039</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11.064</t>
+          <t>11063800.0561705</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.879</t>
+          <t>10879176.8194628</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.262</t>
+          <t>11261888.2898345</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>13140265.9570656</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14.663</t>
+          <t>14662898.0145129</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16.885</t>
+          <t>16884983.3958561</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>19.994</t>
+          <t>19993857.979492</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23.844</t>
+          <t>23843700.6937525</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>27.981</t>
+          <t>27980748.9042045</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26.343</t>
+          <t>26343330.8704586</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6557.77695871151</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6946.302019958</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6204.9692826808</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6121.58531117552</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6896.30219335529</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7062.95367545479</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7389.53435471416</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7817.0880303639</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8623.5190411988</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8916.466981714</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8665.38569481299</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9217.20362468142</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10404.9505148037</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14615.7350793648</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9750.86580452689</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165100.063911897</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166627.361543799</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166428.478600435</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159434.901773193</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159345.846173613</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154872.472297164</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151965.075322506</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155431.38632602</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162400.84363341</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181819.104170112</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194972.17476928</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>216123.280475945</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246566.12261062</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260925.948664287</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>206745.248074987</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1026540.26464382</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>952833.163904722</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>893143.444605372</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>935102.10267758</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>979379.003543264</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1032079.46690763</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>962725.320199983</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955763.627844336</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1072403.15568661</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1217181.97649905</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1266882.63334715</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1370319.5032731</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1584067.48696757</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1572467.00193412</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1266990.40201326</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79383.1595735465</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78954.8129143218</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82956.085228848</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77316.9177633732</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76728.0303058543</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79158.6555055976</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78454.0797237228</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78808.3130253351</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88097.4757854601</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98498.6054383959</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103469.288385499</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110226.29502975</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120857.100325369</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>125950.097420976</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102259.130945622</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>306347.134030943</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318647.798017745</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>305625.325385521</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>329041.618187253</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>372041.402635058</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>416446.989161156</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>410875.240315292</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444064.01402887</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>490524.320562914</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>565081.387530703</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>639948.980236301</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699777.70344674</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>799334.702570303</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>831384.634596738</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>641998.670836341</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21450.7677079101</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20041.8104502434</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19905.7572734703</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19703.9358160778</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18853.9393374286</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20140.9194316792</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20620.2349414723</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21645.883593601</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23951.8681214983</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28060.6435347705</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28389.5594794564</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29938.3955875734</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31473.2255241718</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32705.6753605037</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25779.1739725129</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81882.3669057957</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80515.0404354056</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78587.1798166988</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83151.3582522999</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91907.6454967615</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93295.8525495317</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87898.2551225058</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88677.1094262735</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96889.5090713783</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108980.241649646</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118401.857388055</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127824.532905077</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144195.345626464</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148590.304620083</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110504.607896753</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>531357.754291017</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>526642.411422926</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485556.646167748</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>504440.677890762</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>557611.272168147</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>583418.333269595</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>563953.958415469</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>559118.923447987</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>612967.95273469</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>691587.851522288</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>749892.676153509</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>792370.613926859</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>911915.841766077</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>938666.825931579</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>788453.407632309</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>591766.081018558</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>598389.251186981</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588470.072985973</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>598382.317984894</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>628114.627423488</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>640116.362206438</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>610780.624938002</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>618536.741622824</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>659766.801305357</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>742012.690455261</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>813433.560292041</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>855910.915729787</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>952459.435818154</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>939399.546083298</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816047.950139077</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80883.2669922618</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84566.5777728526</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77848.4287204644</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79851.0185270823</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83296.3408910047</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93365.4032679709</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86614.3426036497</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90283.837988103</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97369.0535010863</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109389.856522087</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115670.498088294</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132011.561563336</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148950.062290394</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165680.532606218</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140744.149754876</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126880.789547734</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123515.797959821</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116153.109987911</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117514.741903709</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132664.887160445</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129324.697341914</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121540.855796568</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123562.70539722</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132296.048320259</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140734.89652173</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147676.070106625</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154322.996521878</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173784.004410328</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170311.539576578</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147032.748271284</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>733145.905435033</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>785529.266413675</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>768844.731698656</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>704260.884312656</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>823580.706193141</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>884095.088234323</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870728.390786956</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>942738.466328405</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1077695.98117054</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>1175841.90862403</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>1108158.47980332</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.146</t>
+          <t>1146118.30610689</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1363926.98553805</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.541</t>
+          <t>1540878.67838488</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1497671.41039881</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7.396</t>
+          <t>7396104.46313576</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.596</t>
+          <t>7596105.0216686</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7.699</t>
+          <t>7699055.25389793</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7.587</t>
+          <t>7586880.91231301</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7.726</t>
+          <t>7725773.14704453</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.179</t>
+          <t>8179473.00702757</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8.348</t>
+          <t>8347547.81273303</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8.493</t>
+          <t>8493235.82858681</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>9.986</t>
+          <t>9986249.66225684</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>11.166</t>
+          <t>11165671.661365</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12.118</t>
+          <t>12117711.271609</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>12.746</t>
+          <t>12746200.5795377</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>14.184</t>
+          <t>14184342.2058904</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>15.538</t>
+          <t>15537673.4473596</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>14.746</t>
+          <t>14746445.1338215</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46469.6951595771</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48571.8230751894</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47412.6024277171</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47939.4775345484</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55094.4679660136</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59107.8281582164</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58587.6055300684</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57665.3346396844</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66001.3776364469</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78634.8964846673</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88198.0465634717</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96174.5799074303</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112686.525256342</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113055.946083083</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97466.6185592101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>498787.232157508</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>506132.948494905</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>479218.449545169</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>499135.918802208</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.537</t>
+          <t>537213.045661723</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580632.167383162</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>551679.337786983</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>562904.685209445</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>634968.248967382</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>723041.126407722</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>776543.554429472</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>878645.781570916</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>991930.866116445</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>982424.680554249</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>754755.499680979</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>2280847.13566858</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2210214.6820699</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>2131537.30123213</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>1977600.53129695</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2105004.09595694</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.226</t>
+          <t>2226049.04820688</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2105048.0683632</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>2055934.91207551</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.239</t>
+          <t>2239306.56924266</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.548</t>
+          <t>2547939.02087754</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.709</t>
+          <t>2708656.52073043</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.887</t>
+          <t>2887217.10438544</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3179924.17111033</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3.571</t>
+          <t>3571170.02788363</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.843</t>
+          <t>2842540.61787208</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1034725.96838052</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1047815.05416768</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1026710.36083217</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>949098.820407138</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1056809.49325917</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1150749.53448337</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1103888.31947627</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.146</t>
+          <t>1146478.8241218</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1243621.15827488</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1464053.13054704</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1544744.48848114</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>1665563.80993104</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>1822580.00889741</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2028596.58865018</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1798611.9070728</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44470.2299372481</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42787.6406217456</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38559.6045285699</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39995.9107670714</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38996.9126438436</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40495.056342876</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37997.5785735917</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38691.0344003613</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42086.800346638</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45103.1873231046</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50948.8176190991</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52339.1352797793</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60555.7148696946</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69810.6043913586</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57076.5407053401</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4960.66056233216</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4426.47517480984</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4219.65502214978</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4561.50057149615</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4616.4033690479</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4984.16215962002</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4672.97203833063</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4766.49611933253</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5398.43306189781</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7067.81216301533</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7738.59734552706</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8163.7457228239</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9332.5700704491</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10434.5430465981</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9652.93109721101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21738.6756253382</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20841.4548915773</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20396.6340798713</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20271.2368375367</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20076.7960244695</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18468.2481255053</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17492.7152897345</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17577.0176815986</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19631.881958319</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23371.0091737108</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24990.9500806336</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27950.6959443573</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33863.4108626736</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34468.300877849</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24168.3131355678</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>617215.797100351</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>649584.52203781</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>655862.440786944</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>688919.858268128</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>739782.856498357</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>778222.884320293</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>775513.75180393</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>780493.344200864</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>843831.137943159</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>971459.299648106</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1090172.27029318</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1131222.34747198</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1254186.71966693</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1454093.55832616</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>1296299.67652657</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2598.70652356826</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2588.09265919899</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2148.1784694281</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2278.91479674516</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2725.23416328149</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3185.70454440644</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2495.75869719706</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2611.55846952112</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2969.28229099837</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3146.67344772498</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3187.33595512157</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3719.76861198699</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4144.71321433078</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4731.45290242625</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3905.09683640545</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212904.16366246</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219195.082563433</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200403.330040077</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218016.428079501</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241865.879216757</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237107.025868461</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237035.81602304</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214653.595077713</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>275136.035975564</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>311326.545088665</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>343799.741916214</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>360245.281319289</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>422406.151212383</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>471790.049007725</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387997.258335346</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>425855.271203875</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>426819.870490539</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>410237.029268785</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>405917.250740977</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>402881.293835936</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>408242.301744765</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>357307.989999481</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>345259.50614939</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>372463.813984156</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>424804.762185494</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>470683.611620264</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>512646.560249468</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>605533.525582239</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>656307.475970411</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>567101.260949578</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82572.9447620218</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81426.2405183095</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73305.2525773091</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76194.5884534344</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79474.3619187831</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86504.720966267</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84282.1541427681</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83686.5141767204</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92651.9961518827</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106530.129067465</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110887.694020923</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118652.725391722</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139863.716646283</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>160076.811105564</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118421.879671345</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154691.929754674</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160767.929340051</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136167.292719161</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120303.038806827</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144088.545828122</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138240.805084583</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134841.586626918</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130073.22781476</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147160.265207798</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157551.077804108</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168400.336594443</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180486.292744569</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>210997.505233222</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239778.315387143</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214252.603363443</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>2301208.50563672</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.287</t>
+          <t>2286646.91422836</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2109534.96003753</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.982</t>
+          <t>1982013.09677964</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1917027.04632992</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.996</t>
+          <t>1995670.79249877</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.985</t>
+          <t>1984654.27973628</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>1970947.6991161</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>2091383.07277281</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2279740.41292603</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2.413</t>
+          <t>2412546.23669959</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.455</t>
+          <t>2454626.14750163</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.811</t>
+          <t>2811026.37949783</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3.067</t>
+          <t>3066809.69092976</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.776</t>
+          <t>2775706.73194178</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67165.2160421663</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67640.3141768564</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61453.9011358044</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59863.8046136845</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59538.6759996479</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59003.5004229473</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57497.1623925228</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56120.9343056049</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60673.2693817556</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67394.2350873802</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74650.4865884568</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81332.6744152452</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99276.4828718809</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110635.057671165</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98306.6909929665</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27219.9549002552</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26241.1488714039</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24293.8920447591</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24422.8828476211</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25734.283573034</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27227.5604455192</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25552.5344129516</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26219.0386575078</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29773.9430060568</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33094.1992418662</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35107.1055240741</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37847.7560391079</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44062.743270672</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51395.2653188322</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42310.6147348767</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113082.520088994</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109970.442989675</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105419.65579303</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109283.78748644</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116555.798107494</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129613.568825182</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120686.983393206</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120888.591823351</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132113.539187964</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149492.842247839</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162698.4093323</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172023.358578095</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199825.107162291</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201232.798072475</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160506.081098603</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>305186.069670528</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318946.185379792</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335636.795976124</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>328496.640755917</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350034.365997635</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>369462.44929418</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338556.591739035</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356009.555362769</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>419944.617427417</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>472653.394074611</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>532337.515543954</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564204.64919255</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>649990.54665918</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>748284.404227359</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>598166.408568557</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318522.776190194</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>315648.976555415</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>310801.742318963</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>307946.946803943</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>329032.100129506</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>364164.04084261</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>324378.939635825</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353008.513667342</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>395205.834887709</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>478898.372477071</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>503107.646590439</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>540940.679752125</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>606648.166568256</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>670020.466329128</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>538789.055349089</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>3267897.14050373</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3279675.8672065</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.258</t>
+          <t>3257887.96484822</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>3323476.34966737</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.527</t>
+          <t>3526717.1676318</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.753</t>
+          <t>3753231.14285567</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.494</t>
+          <t>3493952.95415167</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3410254.81233904</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3610019.55077151</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4.146</t>
+          <t>4146449.33989942</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4.535</t>
+          <t>4534732.54867673</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.815</t>
+          <t>4815170.60620646</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5239920.15240418</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>5.691</t>
+          <t>5690883.66248009</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4.579</t>
+          <t>4578564.89201073</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19.715</t>
+          <t>19714955.2214289</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20.386</t>
+          <t>20385938.115739</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.879</t>
+          <t>20878574.2784809</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>21059616.8273181</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21.852</t>
+          <t>21851899.0834806</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23.015</t>
+          <t>23014605.8312618</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>23.259</t>
+          <t>23259262.3594195</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>24.691</t>
+          <t>24690829.2453563</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>27.595</t>
+          <t>27595256.6421591</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>31.629</t>
+          <t>31628617.6780567</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>34.725</t>
+          <t>34725424.8154645</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>37.873</t>
+          <t>37873202.7962768</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>42.795</t>
+          <t>42795326.0218197</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>48.067</t>
+          <t>48066866.7941296</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>46.663</t>
+          <t>46663323.6127979</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328248</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799158</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
